--- a/files/港岛-香港仔及鸭脷洲-晋环.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-晋环.xlsx
@@ -7237,7 +7237,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -38185,11 +38185,62 @@
     <row r="19" ht="65" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>32/F</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5,000万
+$41,492/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr"/>
+      <c r="D19" s="16" t="inlineStr"/>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1,292万
+$33,736/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1,848万
+$32,260/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$4,820万
+$39,571/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3,152万
+$37,521/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>32&amp;33/F</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr"/>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr"/>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4,190万
@@ -38197,7 +38248,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4,133万
@@ -38205,61 +38256,10 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
-      <c r="H19" s="16" t="inlineStr"/>
-      <c r="I19" s="16" t="inlineStr"/>
-      <c r="J19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5,000万
-$41,492/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr"/>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1,292万
-$33,736/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,848万
-$32,260/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$4,820万
-$39,571/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3,152万
-$37,521/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="E20" s="16" t="inlineStr"/>
+      <c r="F20" s="16" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
+      <c r="H20" s="16" t="inlineStr"/>
       <c r="I20" s="16" t="inlineStr"/>
       <c r="J20" s="16" t="inlineStr"/>
     </row>
@@ -38317,11 +38317,62 @@
     <row r="22" ht="65" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>30/F</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4,880万
+$40,466/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr"/>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1,255万
+$32,770/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1,773万
+$30,935/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3,992万
+$32,778/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2,867万
+$34,131/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="I22" s="16" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>30&amp;31/F</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr"/>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr"/>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4,278万
@@ -38329,7 +38380,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4,076万
@@ -38337,61 +38388,10 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr"/>
-      <c r="G22" s="16" t="inlineStr"/>
-      <c r="H22" s="16" t="inlineStr"/>
-      <c r="I22" s="16" t="inlineStr"/>
-      <c r="J22" s="16" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4,880万
-$40,466/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr"/>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1,255万
-$32,770/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1,773万
-$30,935/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3,992万
-$32,778/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2,867万
-$34,131/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="E23" s="16" t="inlineStr"/>
+      <c r="F23" s="16" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr"/>
+      <c r="H23" s="16" t="inlineStr"/>
       <c r="I23" s="16" t="inlineStr"/>
       <c r="J23" s="16" t="inlineStr"/>
     </row>
@@ -38581,10 +38581,40 @@
     <row r="28" ht="65" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>26&amp;27/F</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr"/>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4,630万
+$35,836/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3,998万
+$30,947/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr"/>
+      <c r="F28" s="16" t="inlineStr"/>
+      <c r="G28" s="16" t="inlineStr"/>
+      <c r="H28" s="16" t="inlineStr"/>
+      <c r="I28" s="16" t="inlineStr"/>
+      <c r="J28" s="16" t="inlineStr"/>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>26/F</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4,840万
@@ -38592,9 +38622,9 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr"/>
-      <c r="D28" s="16" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr"/>
+      <c r="D29" s="16" t="inlineStr"/>
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1,288万
@@ -38602,7 +38632,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1,789万
@@ -38610,7 +38640,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3,664万
@@ -38618,7 +38648,7 @@
 (24年-10月)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2,810万
@@ -38626,36 +38656,6 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr"/>
-      <c r="J28" s="16" t="inlineStr"/>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>26&amp;27/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr"/>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4,630万
-$35,836/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3,998万
-$30,947/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr"/>
-      <c r="G29" s="16" t="inlineStr"/>
-      <c r="H29" s="16" t="inlineStr"/>
       <c r="I29" s="16" t="inlineStr"/>
       <c r="J29" s="16" t="inlineStr"/>
     </row>
@@ -39136,7 +39136,7 @@
           <t>E | 581呎 (2房)
 $1,795万
 $30,898/呎
-(26年-03月)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
